--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36FB46DC-4F67-45D2-84AC-3255CA85617C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0F4CD518-7060-4028-BA9F-44440330CA89}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停并播放使用恢复牌的弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BUG：b11牌的效果在未断裂而不是断裂时生效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,6 +178,14 @@
   </si>
   <si>
     <t>恢复牌问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在双方玩家初始手牌内各加入一张恢复。将恢复变为固定牌。将恢复踢出所有卡池。取消消耗，将所有卡牌改为固定，并改动内容。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,9 +232,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,14 +573,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE58BE6B-4D4C-4E03-8383-44852D32A7D6}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.625" customWidth="1"/>
     <col min="3" max="3" width="84.25" customWidth="1"/>
+    <col min="4" max="4" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -587,7 +595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -601,7 +609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -615,7 +623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -629,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -643,7 +651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -657,7 +665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -671,7 +679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -685,7 +693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -699,7 +707,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -709,11 +717,11 @@
       <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -721,10 +729,10 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -732,13 +740,13 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -746,27 +754,27 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -774,10 +782,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36FB46DC-4F67-45D2-84AC-3255CA85617C}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C430710F-FE94-443F-B119-BF2332D95B7C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0F4CD518-7060-4028-BA9F-44440330CA89}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,18 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郭修齐没有保存旧版的卡牌设计excel文档</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要另一个人把当前云端的设计excel新版保存，改名并发到微信群里。等郭修齐把新的设计excel推到云端后，把微信群里的文件加入doc文件夹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,31 +125,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>设计，程序，美术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>教学弹窗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BUG：b11牌的效果在未断裂而不是断裂时生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>a1牌效果不理想。1号怪的5点血应要求玩家在用a1牌时撞击两次，但由于a1牌判定过快，效果不理想</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>将a1牌的效果改为1.5秒判定一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗牌与固定牌区别不明显</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非重要问题，留至优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -254,6 +226,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -599,28 +575,19 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -628,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -642,13 +609,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -656,13 +623,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -670,13 +637,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -684,13 +651,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -698,13 +665,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -715,63 +682,48 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -779,16 +731,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C430710F-FE94-443F-B119-BF2332D95B7C}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC31091-50FE-409F-8748-FF0222D62F35}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0F4CD518-7060-4028-BA9F-44440330CA89}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,14 +90,6 @@
   </si>
   <si>
     <t>需要修改代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新玩家不知道要在断裂时用恢复牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂时，当玩家当前手牌是恢复，将其高亮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -622,15 +614,6 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -640,10 +623,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -654,10 +637,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -668,10 +651,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -679,13 +662,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -701,10 +684,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -717,13 +700,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
         <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -734,13 +717,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC31091-50FE-409F-8748-FF0222D62F35}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D697A1-E47B-493D-AE2F-21F859B82E79}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0F4CD518-7060-4028-BA9F-44440330CA89}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,22 +77,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已修改，需要更多测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>程序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>肉体很容易粘在墙上，发现对体验打击非常大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要修改代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -101,42 +85,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>卡牌内容难读</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在卡牌详细内容中，不再显示“攻击牌”和“其他牌”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>拦网体验问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>减短把肉体拉出拦网所需要的距离</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>教学弹窗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a1牌效果不理想。1号怪的5点血应要求玩家在用a1牌时撞击两次，但由于a1牌判定过快，效果不理想</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>将a1牌的效果改为1.5秒判定一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否加入boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>需要讨论</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,6 +110,10 @@
   </si>
   <si>
     <t>在双方玩家初始手牌内各加入一张恢复。将恢复变为固定牌。将恢复踢出所有卡池。取消消耗，将所有卡牌改为固定，并改动内容。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,11 +527,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
@@ -593,26 +552,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -623,24 +563,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -651,7 +577,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -662,51 +588,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -717,13 +605,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{71DA3901-4FB6-4295-A647-874DCCA459D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D697A1-E47B-493D-AE2F-21F859B82E79}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{0F4CD518-7060-4028-BA9F-44440330CA89}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,122 +22,441 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>解决方法·</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计，程序</t>
+  </si>
+  <si>
+    <t>测试中发现打击反馈不足</t>
+  </si>
+  <si>
+    <t>在使用攻击牌时加入镜头晃动。在敌人拥有美术后，为死亡的敌人添加粒子特效</t>
   </si>
   <si>
     <t>设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试中发现打击反馈不足</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设计，程序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在使用攻击牌时加入镜头晃动。在敌人拥有美术后，为死亡的敌人添加粒子特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>难度曲线不足，难度会突然升高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要测试</t>
+  </si>
+  <si>
+    <t>程序</t>
+  </si>
+  <si>
+    <t>将测试用的作弊按键由空格改为del</t>
   </si>
   <si>
     <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拦网体验问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全</t>
   </si>
   <si>
     <t>教学弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
+  </si>
+  <si>
+    <t>恢复牌问题</t>
   </si>
   <si>
     <t>需要讨论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复牌问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>在双方玩家初始手牌内各加入一张恢复。将恢复变为固定牌。将恢复踢出所有卡池。取消消耗，将所有卡牌改为固定，并改动内容。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -154,9 +464,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -168,24 +720,64 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -231,7 +823,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -264,26 +856,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -316,23 +891,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -494,26 +1052,21 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE58BE6B-4D4C-4E03-8383-44852D32A7D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="18.625" customWidth="1"/>
     <col min="3" max="3" width="84.25" customWidth="1"/>
     <col min="4" max="4" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,95 +1080,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="48" customHeight="1" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>编号</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>将测试用的作弊按键由空格改为del</t>
+  </si>
+  <si>
+    <t>给牌堆做堆叠</t>
   </si>
   <si>
     <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
@@ -102,14 +105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,148 +563,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1119,6 +1115,17 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
@@ -1127,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1141,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1152,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1169,13 +1176,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>编号</t>
   </si>
@@ -84,6 +84,15 @@
   </si>
   <si>
     <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
+  </si>
+  <si>
+    <t>每一次断裂时，双方的恢复牌都会被拉到顶端。而不是第一次断裂的引导内</t>
+  </si>
+  <si>
+    <t>bug</t>
+  </si>
+  <si>
+    <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
   </si>
   <si>
     <t>恢复牌问题</t>
@@ -1168,6 +1177,34 @@
         <v>18</v>
       </c>
     </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
@@ -1176,13 +1213,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>编号</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
+  </si>
+  <si>
+    <t>回血（a5）没效果，打出以后没有回血</t>
   </si>
   <si>
     <t>恢复牌问题</t>
@@ -1205,6 +1208,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
@@ -1213,13 +1230,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>编号</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>回血（a5）没效果，打出以后没有回血</t>
+  </si>
+  <si>
+    <t>P2的卡池里需要有一张恢复</t>
+  </si>
+  <si>
+    <t>修改代码</t>
   </si>
   <si>
     <t>恢复牌问题</t>
@@ -1222,6 +1228,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
@@ -1230,13 +1250,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C22A3ADA25FDFCB3C48CF088311B480589004C72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F49CF1-6BBD-41D5-82CD-0A8F7553E3A9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>编号</t>
   </si>
@@ -47,6 +41,15 @@
     <t>解决方法·</t>
   </si>
   <si>
+    <t>程序</t>
+  </si>
+  <si>
+    <t>游戏开始时，若P2换牌，换掉第一张恢复后不会有CD。只会在游戏开始时出现的bug</t>
+  </si>
+  <si>
+    <t>bug</t>
+  </si>
+  <si>
     <t>设计，程序</t>
   </si>
   <si>
@@ -65,9 +68,6 @@
     <t>需要测试</t>
   </si>
   <si>
-    <t>程序</t>
-  </si>
-  <si>
     <t>将测试用的作弊按键由空格改为del</t>
   </si>
   <si>
@@ -92,10 +92,7 @@
     <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
   </si>
   <si>
-    <t>每一次断裂时，双方的恢复牌都会被拉到顶端。而不是第一次断裂的引导内</t>
-  </si>
-  <si>
-    <t>bug</t>
+    <t>每一次断裂时，恢复牌都会被拉到顶端。而不是第一次断裂的引导内。在玩家主动断裂时，只会拉对应玩家的恢复牌</t>
   </si>
   <si>
     <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
@@ -117,25 +114,19 @@
   </si>
   <si>
     <t>在双方玩家初始手牌内各加入一张恢复。将恢复变为固定牌。将恢复踢出所有卡池。取消消耗，将所有卡牌改为固定，并改动内容。</t>
-  </si>
-  <si>
-    <t>程序</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏开始时，若P2换牌，换掉第一张恢复后不会有CD。只会在游戏开始时出现的bug</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bug</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,27 +138,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -175,9 +488,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -185,24 +740,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -480,21 +1079,21 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="84.25" customWidth="1"/>
+    <col min="3" max="3" width="96.625" customWidth="1"/>
     <col min="4" max="4" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,187 +1107,187 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>编号</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
+  </si>
+  <si>
+    <t>没有把肉体拉到终点线然后胜利的功能</t>
   </si>
   <si>
     <t>拦网体验问题</t>
@@ -126,14 +129,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,133 +602,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -740,7 +736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1185,6 +1181,17 @@
         <v>16</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
@@ -1193,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1204,13 +1211,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1221,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -1235,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -1249,7 +1256,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -1263,10 +1270,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1277,13 +1284,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>编号</t>
   </si>
@@ -44,70 +44,67 @@
     <t>程序</t>
   </si>
   <si>
-    <t>游戏开始时，若P2换牌，换掉第一张恢复后不会有CD。只会在游戏开始时出现的bug</t>
+    <t>需要给拿牌界面加一个退出键</t>
+  </si>
+  <si>
+    <t>设计，程序</t>
+  </si>
+  <si>
+    <t>测试中发现打击反馈不足</t>
+  </si>
+  <si>
+    <t>在使用攻击牌时加入镜头晃动。在敌人拥有美术后，为死亡的敌人添加粒子特效</t>
+  </si>
+  <si>
+    <t>将测试用的作弊按键由空格改为del</t>
+  </si>
+  <si>
+    <t>给牌堆做堆叠</t>
+  </si>
+  <si>
+    <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
+  </si>
+  <si>
+    <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
+  </si>
+  <si>
+    <t>没有把肉体拉到终点线然后胜利的功能</t>
+  </si>
+  <si>
+    <t>拦网体验问题</t>
+  </si>
+  <si>
+    <t>需要测试</t>
+  </si>
+  <si>
+    <t>全</t>
+  </si>
+  <si>
+    <t>教学弹窗</t>
+  </si>
+  <si>
+    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
+  </si>
+  <si>
+    <t>每一次断裂时，恢复牌都会被拉到顶端。而不是第一次断裂的引导内。在玩家主动断裂时，只会拉对应玩家的恢复牌</t>
   </si>
   <si>
     <t>bug</t>
   </si>
   <si>
-    <t>设计，程序</t>
-  </si>
-  <si>
-    <t>测试中发现打击反馈不足</t>
-  </si>
-  <si>
-    <t>在使用攻击牌时加入镜头晃动。在敌人拥有美术后，为死亡的敌人添加粒子特效</t>
+    <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
+  </si>
+  <si>
+    <t>回血（a5）没效果，打出以后没有回血</t>
+  </si>
+  <si>
+    <t>P2的卡池里需要有一张恢复</t>
+  </si>
+  <si>
+    <t>修改代码</t>
   </si>
   <si>
     <t>设计</t>
-  </si>
-  <si>
-    <t>难度曲线不足，难度会突然升高</t>
-  </si>
-  <si>
-    <t>需要测试</t>
-  </si>
-  <si>
-    <t>将测试用的作弊按键由空格改为del</t>
-  </si>
-  <si>
-    <t>给牌堆做堆叠</t>
-  </si>
-  <si>
-    <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
-  </si>
-  <si>
-    <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
-  </si>
-  <si>
-    <t>没有把肉体拉到终点线然后胜利的功能</t>
-  </si>
-  <si>
-    <t>拦网体验问题</t>
-  </si>
-  <si>
-    <t>全</t>
-  </si>
-  <si>
-    <t>教学弹窗</t>
-  </si>
-  <si>
-    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
-  </si>
-  <si>
-    <t>每一次断裂时，恢复牌都会被拉到顶端。而不是第一次断裂的引导内。在玩家主动断裂时，只会拉对应玩家的恢复牌</t>
-  </si>
-  <si>
-    <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
-  </si>
-  <si>
-    <t>回血（a5）没效果，打出以后没有回血</t>
-  </si>
-  <si>
-    <t>P2的卡池里需要有一张恢复</t>
-  </si>
-  <si>
-    <t>修改代码</t>
   </si>
   <si>
     <t>恢复牌问题</t>
@@ -1113,36 +1110,20 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1153,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1164,7 +1145,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1172,13 +1153,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1189,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1197,13 +1178,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:5">
@@ -1211,13 +1192,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1228,10 +1209,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1242,10 +1223,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1256,10 +1237,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1267,13 +1248,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1281,16 +1262,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>28</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>编号</t>
   </si>
@@ -50,70 +50,10 @@
     <t>设计，程序</t>
   </si>
   <si>
-    <t>测试中发现打击反馈不足</t>
-  </si>
-  <si>
-    <t>在使用攻击牌时加入镜头晃动。在敌人拥有美术后，为死亡的敌人添加粒子特效</t>
-  </si>
-  <si>
-    <t>将测试用的作弊按键由空格改为del</t>
-  </si>
-  <si>
-    <t>给牌堆做堆叠</t>
-  </si>
-  <si>
     <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
   </si>
   <si>
     <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
-  </si>
-  <si>
-    <t>没有把肉体拉到终点线然后胜利的功能</t>
-  </si>
-  <si>
-    <t>拦网体验问题</t>
-  </si>
-  <si>
-    <t>需要测试</t>
-  </si>
-  <si>
-    <t>全</t>
-  </si>
-  <si>
-    <t>教学弹窗</t>
-  </si>
-  <si>
-    <t>在游戏开始时加入键位的教学弹窗，在首次断裂时暂停，将玩家手中牌切至恢复，并播放使用恢复牌的弹窗</t>
-  </si>
-  <si>
-    <t>每一次断裂时，恢复牌都会被拉到顶端。而不是第一次断裂的引导内。在玩家主动断裂时，只会拉对应玩家的恢复牌</t>
-  </si>
-  <si>
-    <t>bug</t>
-  </si>
-  <si>
-    <t>恢复牌仍在卡池内，但恢复牌不应在任何卡池内。游戏内唯二两张恢复是两个玩家开局的恢复</t>
-  </si>
-  <si>
-    <t>回血（a5）没效果，打出以后没有回血</t>
-  </si>
-  <si>
-    <t>P2的卡池里需要有一张恢复</t>
-  </si>
-  <si>
-    <t>修改代码</t>
-  </si>
-  <si>
-    <t>设计</t>
-  </si>
-  <si>
-    <t>恢复牌问题</t>
-  </si>
-  <si>
-    <t>需要讨论</t>
-  </si>
-  <si>
-    <t>在双方玩家初始手牌内各加入一张恢复。将恢复变为固定牌。将恢复踢出所有卡池。取消消耗，将所有卡牌改为固定，并改动内容。</t>
   </si>
 </sst>
 </file>
@@ -1078,15 +1018,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="18.625" customWidth="1"/>
     <col min="3" max="3" width="96.625" customWidth="1"/>
     <col min="4" max="4" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1112,7 +1052,7 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1126,153 +1066,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:5">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
+    <row r="10" ht="48" customHeight="1" spans="1:4">
+      <c r="D10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>编号</t>
   </si>
@@ -45,15 +45,6 @@
   </si>
   <si>
     <t>需要给拿牌界面加一个退出键</t>
-  </si>
-  <si>
-    <t>设计，程序</t>
-  </si>
-  <si>
-    <t>为增强打击反馈和策略性，小梦提出可以让技能清除弹幕</t>
-  </si>
-  <si>
-    <t>使a1牌清除范围内的弹幕，a2牌清除玩家碰到的弹幕，a4、b7清除所有（场景内所有）弹幕</t>
   </si>
 </sst>
 </file>
@@ -1052,20 +1043,6 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="10" ht="48" customHeight="1" spans="1:4">
       <c r="D10" s="2"/>
     </row>

--- a/doc/策划问题.xlsx
+++ b/doc/策划问题.xlsx
@@ -27,24 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>问题</t>
-  </si>
-  <si>
-    <t>解决方法·</t>
-  </si>
-  <si>
-    <t>程序</t>
-  </si>
-  <si>
-    <t>需要给拿牌界面加一个退出键</t>
+    <t>见微信群</t>
   </si>
 </sst>
 </file>
@@ -1021,26 +1006,10 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4">
